--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="409">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>Organization.identifier</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -971,6 +974,81 @@
   </si>
   <si>
     <t>Österreichisches Bundesministerium für Gesundheit</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT</t>
+  </si>
+  <si>
+    <t>SVT</t>
+  </si>
+  <si>
+    <t>CodeSystem: e-card Sozialversicherungsträger Codesystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>http://svc.co.at/CodeSystem/ecard-svt-cs</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:SVT.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT</t>
+  </si>
+  <si>
+    <t>LSVT</t>
+  </si>
+  <si>
+    <t>L-Codes der Sozialversicherungsträger</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.system</t>
+  </si>
+  <si>
+    <t>http://example.org/lsvt-code</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:LSVT.assigner</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1517,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK87"/>
+  <dimension ref="A1:AK105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.37109375" customWidth="true" bestFit="true"/>
@@ -2627,7 +2705,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>75</v>
@@ -2642,17 +2720,17 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2689,14 +2767,14 @@
         <v>20</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>138</v>
@@ -2708,24 +2786,24 @@
         <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2747,17 +2825,17 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2815,21 +2893,21 @@
         <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2855,10 +2933,10 @@
         <v>83</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2909,7 +2987,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2918,7 +2996,7 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>20</v>
@@ -2929,10 +3007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2961,7 +3039,7 @@
         <v>128</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>130</v>
@@ -3002,19 +3080,19 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -3034,10 +3112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3063,16 +3141,16 @@
         <v>101</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3100,10 +3178,10 @@
         <v>105</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3121,7 +3199,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3141,10 +3219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3167,19 +3245,19 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3204,13 +3282,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3228,7 +3306,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3248,10 +3326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3277,29 +3355,29 @@
         <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>20</v>
@@ -3335,7 +3413,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3350,15 +3428,15 @@
         <v>93</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3381,16 +3459,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3404,7 +3482,7 @@
         <v>20</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>20</v>
@@ -3440,7 +3518,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3449,21 +3527,21 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3486,13 +3564,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3543,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3558,15 +3636,15 @@
         <v>93</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3589,16 +3667,16 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3648,7 +3726,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3663,15 +3741,15 @@
         <v>93</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3697,10 +3775,10 @@
         <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3751,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3760,7 +3838,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>20</v>
@@ -3771,10 +3849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3803,7 +3881,7 @@
         <v>128</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>130</v>
@@ -3844,19 +3922,19 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3876,10 +3954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3902,16 +3980,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3961,7 +4039,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3970,7 +4048,7 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>93</v>
@@ -3981,10 +4059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4010,13 +4088,13 @@
         <v>95</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4042,13 +4120,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4066,7 +4144,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4086,10 +4164,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4112,16 +4190,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4171,7 +4249,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4180,7 +4258,7 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>93</v>
@@ -4191,10 +4269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4217,16 +4295,16 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4234,7 +4312,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>20</v>
@@ -4276,7 +4354,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4285,7 +4363,7 @@
         <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>93</v>
@@ -4296,13 +4374,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
@@ -4324,17 +4402,17 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4392,21 +4470,21 @@
         <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4432,10 +4510,10 @@
         <v>83</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4486,7 +4564,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4495,7 +4573,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>20</v>
@@ -4506,10 +4584,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4538,7 +4616,7 @@
         <v>128</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>130</v>
@@ -4579,19 +4657,19 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4611,10 +4689,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4640,16 +4718,16 @@
         <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -4677,10 +4755,10 @@
         <v>105</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -4698,7 +4776,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4718,10 +4796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4744,19 +4822,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4781,13 +4859,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -4805,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4825,10 +4903,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4854,29 +4932,29 @@
         <v>95</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>20</v>
@@ -4912,7 +4990,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4927,15 +5005,15 @@
         <v>93</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4958,16 +5036,16 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4981,7 +5059,7 @@
         <v>20</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>20</v>
@@ -5017,7 +5095,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5026,21 +5104,21 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5063,13 +5141,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5120,7 +5198,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5135,15 +5213,15 @@
         <v>93</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5166,16 +5244,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5225,7 +5303,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5240,15 +5318,15 @@
         <v>93</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5274,10 +5352,10 @@
         <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5328,7 +5406,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5337,7 +5415,7 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
@@ -5348,10 +5426,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5380,7 +5458,7 @@
         <v>128</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>130</v>
@@ -5421,19 +5499,19 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5453,10 +5531,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5479,16 +5557,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5538,7 +5616,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5547,7 +5625,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>93</v>
@@ -5558,10 +5636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5587,13 +5665,13 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5619,13 +5697,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -5643,7 +5721,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5663,10 +5741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5689,16 +5767,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5748,7 +5826,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5757,7 +5835,7 @@
         <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>93</v>
@@ -5768,10 +5846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5794,16 +5872,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5811,7 +5889,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>20</v>
@@ -5853,7 +5931,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5862,7 +5940,7 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>93</v>
@@ -5873,13 +5951,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
@@ -5901,17 +5979,17 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -5969,21 +6047,21 @@
         <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6009,10 +6087,10 @@
         <v>83</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6063,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6072,7 +6150,7 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>20</v>
@@ -6083,10 +6161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6115,7 +6193,7 @@
         <v>128</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>130</v>
@@ -6156,19 +6234,19 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6188,10 +6266,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6217,16 +6295,16 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6254,10 +6332,10 @@
         <v>105</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6275,7 +6353,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6295,10 +6373,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6321,19 +6399,19 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6358,13 +6436,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6382,7 +6460,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6402,10 +6480,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6431,29 +6509,29 @@
         <v>95</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -6489,7 +6567,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6504,15 +6582,15 @@
         <v>93</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6535,16 +6613,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6558,7 +6636,7 @@
         <v>20</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>20</v>
@@ -6594,7 +6672,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6603,21 +6681,21 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6640,13 +6718,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6697,7 +6775,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6712,15 +6790,15 @@
         <v>93</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6743,16 +6821,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6802,7 +6880,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6817,15 +6895,15 @@
         <v>93</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6851,10 +6929,10 @@
         <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6905,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6914,7 +6992,7 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>20</v>
@@ -6925,10 +7003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6957,7 +7035,7 @@
         <v>128</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>130</v>
@@ -6998,19 +7076,19 @@
         <v>20</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7030,10 +7108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7056,16 +7134,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7115,7 +7193,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7124,7 +7202,7 @@
         <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>93</v>
@@ -7135,10 +7213,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7164,13 +7242,13 @@
         <v>95</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7196,13 +7274,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7220,7 +7298,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7240,10 +7318,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7266,16 +7344,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7325,7 +7403,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7334,7 +7412,7 @@
         <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>93</v>
@@ -7345,10 +7423,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7371,16 +7449,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7388,7 +7466,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>20</v>
@@ -7430,7 +7508,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7439,7 +7517,7 @@
         <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>93</v>
@@ -7450,13 +7528,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>20</v>
@@ -7478,17 +7556,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7546,21 +7624,21 @@
         <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7586,10 +7664,10 @@
         <v>83</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7640,7 +7718,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -7649,7 +7727,7 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>20</v>
@@ -7660,10 +7738,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7692,7 +7770,7 @@
         <v>128</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>130</v>
@@ -7733,19 +7811,19 @@
         <v>20</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -7765,10 +7843,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7794,16 +7872,16 @@
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -7831,10 +7909,10 @@
         <v>105</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -7852,7 +7930,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -7872,10 +7950,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7898,19 +7976,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -7935,13 +8013,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -7959,7 +8037,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -7979,10 +8057,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8008,29 +8086,29 @@
         <v>95</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>20</v>
@@ -8066,7 +8144,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8081,15 +8159,15 @@
         <v>93</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8112,16 +8190,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8135,7 +8213,7 @@
         <v>20</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>20</v>
@@ -8171,7 +8249,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8180,21 +8258,21 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8217,13 +8295,13 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8274,7 +8352,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8289,15 +8367,15 @@
         <v>93</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8320,16 +8398,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8379,7 +8457,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8394,15 +8472,15 @@
         <v>93</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8428,10 +8506,10 @@
         <v>83</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8482,7 +8560,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -8491,7 +8569,7 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>20</v>
@@ -8502,10 +8580,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8534,7 +8612,7 @@
         <v>128</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>130</v>
@@ -8575,19 +8653,19 @@
         <v>20</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -8607,10 +8685,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8633,16 +8711,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8692,7 +8770,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -8701,7 +8779,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>93</v>
@@ -8712,10 +8790,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8741,13 +8819,13 @@
         <v>95</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8773,13 +8851,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -8797,7 +8875,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -8817,10 +8895,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8843,16 +8921,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8902,7 +8980,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -8911,7 +8989,7 @@
         <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>93</v>
@@ -8922,10 +9000,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8948,16 +9026,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8965,7 +9043,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>20</v>
@@ -9007,7 +9085,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
@@ -9016,7 +9094,7 @@
         <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>93</v>
@@ -9027,18 +9105,20 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>81</v>
@@ -9047,32 +9127,28 @@
         <v>20</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>309</v>
+        <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>313</v>
+        <v>143</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>314</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>20</v>
       </c>
@@ -9116,30 +9192,30 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>308</v>
+        <v>138</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>315</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>316</v>
+        <v>151</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9150,7 +9226,7 @@
         <v>74</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -9159,23 +9235,19 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>317</v>
+        <v>152</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>20</v>
       </c>
@@ -9184,7 +9256,7 @@
         <v>20</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>20</v>
@@ -9199,11 +9271,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -9221,41 +9295,41 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>316</v>
+        <v>154</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>324</v>
+        <v>157</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -9264,23 +9338,21 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>325</v>
+        <v>128</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>326</v>
+        <v>158</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
       </c>
@@ -9316,42 +9388,42 @@
         <v>20</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>330</v>
+        <v>163</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9362,31 +9434,31 @@
         <v>74</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>331</v>
+        <v>164</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>332</v>
+        <v>165</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>333</v>
+        <v>166</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>334</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -9411,13 +9483,13 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -9435,13 +9507,13 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>330</v>
+        <v>170</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
@@ -9455,10 +9527,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>335</v>
+        <v>172</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9481,17 +9553,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>336</v>
+        <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>337</v>
+        <v>174</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -9516,13 +9590,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -9540,7 +9614,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>335</v>
+        <v>181</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -9560,10 +9634,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9571,10 +9645,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -9583,35 +9657,35 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>341</v>
+        <v>95</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>343</v>
+        <v>185</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>344</v>
+        <v>186</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>345</v>
+        <v>187</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>20</v>
@@ -9647,30 +9721,30 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>346</v>
+        <v>93</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>347</v>
+        <v>193</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9693,18 +9767,18 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>348</v>
+        <v>260</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -9716,7 +9790,7 @@
         <v>20</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>20</v>
@@ -9752,7 +9826,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -9761,21 +9835,21 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>323</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>351</v>
+        <v>203</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9786,7 +9860,7 @@
         <v>74</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -9795,21 +9869,19 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>352</v>
+        <v>204</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>353</v>
+        <v>205</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>354</v>
+        <v>206</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>20</v>
       </c>
@@ -9857,13 +9929,13 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>351</v>
+        <v>207</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
@@ -9872,15 +9944,15 @@
         <v>93</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9891,7 +9963,7 @@
         <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -9900,18 +9972,20 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>357</v>
+        <v>211</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>358</v>
+        <v>212</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -9960,13 +10034,13 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>356</v>
+        <v>215</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
@@ -9975,23 +10049,25 @@
         <v>93</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>81</v>
@@ -10003,19 +10079,21 @@
         <v>20</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
       </c>
@@ -10063,41 +10141,41 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>20</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -10109,17 +10187,15 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -10168,19 +10244,19 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -10188,14 +10264,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>362</v>
+        <v>157</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>363</v>
+        <v>126</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10208,26 +10284,24 @@
         <v>20</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>127</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>364</v>
+        <v>128</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>20</v>
       </c>
@@ -10263,19 +10337,19 @@
         <v>20</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>366</v>
+        <v>161</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10295,10 +10369,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10309,29 +10383,31 @@
         <v>74</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>368</v>
+        <v>164</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>370</v>
+        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -10356,13 +10432,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -10380,13 +10456,13 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>367</v>
+        <v>170</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
@@ -10400,10 +10476,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>371</v>
+        <v>172</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10411,7 +10487,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>81</v>
@@ -10423,19 +10499,23 @@
         <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>372</v>
+        <v>174</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
       </c>
@@ -10459,13 +10539,13 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>374</v>
+        <v>178</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>375</v>
+        <v>179</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -10483,10 +10563,10 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>371</v>
+        <v>181</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>81</v>
@@ -10503,10 +10583,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>376</v>
+        <v>329</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>376</v>
+        <v>183</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10514,7 +10594,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>81</v>
@@ -10526,33 +10606,35 @@
         <v>20</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>379</v>
+        <v>187</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>20</v>
@@ -10588,7 +10670,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>376</v>
+        <v>190</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10603,15 +10685,15 @@
         <v>93</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>380</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>380</v>
+        <v>193</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10631,18 +10713,20 @@
         <v>20</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>381</v>
+        <v>260</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -10655,7 +10739,7 @@
         <v>20</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>20</v>
@@ -10691,7 +10775,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>380</v>
+        <v>199</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -10700,12 +10784,1904 @@
         <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q90" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="R90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y91" s="2"/>
+      <c r="Z91" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AK105" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-SVOrganization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
